--- a/Result/profitability/9934.xlsx
+++ b/Result/profitability/9934.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.53</v>
       </c>
       <c r="M2" t="n">
-        <v>0.105</v>
+        <v>0.1612499999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>33.43125</v>
+        <v>34.02375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.19</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1274999999999999</v>
+        <v>0.1474999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>33.075</v>
+        <v>33.885</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.34</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1325</v>
+        <v>0.1825</v>
       </c>
       <c r="N4" t="n">
-        <v>32.22625</v>
+        <v>32.79875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.02</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1274999999999999</v>
+        <v>0.16625</v>
       </c>
       <c r="N5" t="n">
-        <v>31.7225</v>
+        <v>32.0975</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.28</v>
       </c>
       <c r="M6" t="n">
-        <v>0.14375</v>
+        <v>0.2425</v>
       </c>
       <c r="N6" t="n">
-        <v>30.9875</v>
+        <v>31.41125</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,13 +1264,13 @@
         <v>0.26</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2175</v>
+        <v>0.2949999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>30.4625</v>
+        <v>31.21625</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,13 +1282,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" t="n">
         <v>98.2</v>
@@ -1391,10 +1391,10 @@
         <v>0.54</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3049999999999999</v>
+        <v>0.3275</v>
       </c>
       <c r="N8" t="n">
-        <v>30.31</v>
+        <v>30.83375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>9934</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>4833</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2977</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1856</v>
+      </c>
+      <c r="F75" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="G75" t="n">
+        <v>267</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>5.53%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>2</v>
+      </c>
+      <c r="J75" t="n">
+        <v>270</v>
+      </c>
+      <c r="K75" t="n">
+        <v>191</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.09624999999999995</v>
+      </c>
+      <c r="N75" t="n">
+        <v>34.34875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.6428571428571428</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>4.189999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.122478807366267</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.3100000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>2.066666666666667</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.0847457627118644</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
